--- a/V5.0_双人执行工作区/B_AI交付/02_看板/DB06/DB06_RECONCILIATION_V50.xlsx
+++ b/V5.0_双人执行工作区/B_AI交付/02_看板/DB06/DB06_RECONCILIATION_V50.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对账结果" sheetId="1" r:id="R113e2e087198443b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对账结果" sheetId="1" r:id="R301142ca697845e6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -160,7 +160,7 @@
         <x:color rgb="FFD0021B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDEBEC"/>
         </x:patternFill>
       </x:fill>
@@ -171,7 +171,7 @@
         <x:color rgb="FF8A5A00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4DF"/>
         </x:patternFill>
       </x:fill>
@@ -182,7 +182,7 @@
         <x:color rgb="FF8A5A00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4DF"/>
         </x:patternFill>
       </x:fill>
@@ -193,7 +193,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -422,7 +422,7 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>DB06 页面对账与验收结果｜2026-08-30</x:v>
+        <x:v>DB06 页面对账与验收结果｜2026-08-31</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -498,16 +498,16 @@
         <x:v>默认月份下1条</x:v>
       </x:c>
       <x:c r="C5" s="23" t="str">
-        <x:v>仍为660条</x:v>
+        <x:v>1条（2025-12-31）</x:v>
       </x:c>
       <x:c r="D5" s="23" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS_A_FIX</x:v>
       </x:c>
       <x:c r="E5" s="23" t="str">
-        <x:v>A核查日期维→MVP周期表关系；修复后B复测</x:v>
+        <x:v>A已修复双向关系并清缓存；B独立复测后签收</x:v>
       </x:c>
       <x:c r="F5" s="23" t="str">
-        <x:v>DB06_月份联动异常_C01为660_C03为360_20260830.png</x:v>
+        <x:v>DB06_关系修复待B复核_20260831.md</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
@@ -598,16 +598,16 @@
         <x:v>2020-04、2023-10、2025-12均与辅助表一致</x:v>
       </x:c>
       <x:c r="C10" s="23" t="str">
-        <x:v>关系阻塞，未完成</x:v>
+        <x:v>A预检三个月份：组件1=1、组件3=360</x:v>
       </x:c>
       <x:c r="D10" s="23" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>READY_B_REVIEW</x:v>
       </x:c>
       <x:c r="E10" s="23" t="str">
-        <x:v>A修复关系后B复测并截图</x:v>
+        <x:v>B独立复测并签收</x:v>
       </x:c>
       <x:c r="F10" s="23" t="str">
-        <x:v>待补三个月份证据</x:v>
+        <x:v>DB06_关系修复待B复核_20260831.md</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="32" customHeight="1">
@@ -618,16 +618,16 @@
         <x:v>典型筛选均≤10秒</x:v>
       </x:c>
       <x:c r="C11" s="23" t="str">
-        <x:v>未正式计时</x:v>
+        <x:v>用户明确不要求性能计时截图</x:v>
       </x:c>
       <x:c r="D11" s="23" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>WAIVED_BY_USER</x:v>
       </x:c>
       <x:c r="E11" s="23" t="str">
-        <x:v>B补冷/热性能三次</x:v>
+        <x:v>无需补性能截图</x:v>
       </x:c>
       <x:c r="F11" s="23" t="str">
-        <x:v>待补性能证据</x:v>
+        <x:v>用户指令（2026-08-30）</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="32" customHeight="1">
@@ -638,16 +638,16 @@
         <x:v>A签PASS/FAIL/BLOCKED</x:v>
       </x:c>
       <x:c r="C12" s="23" t="str">
-        <x:v>尚未复核</x:v>
+        <x:v>已核查关系、保存、清缓存并实测</x:v>
       </x:c>
       <x:c r="D12" s="23" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PASS_A / READY_B_REVIEW</x:v>
       </x:c>
       <x:c r="E12" s="23" t="str">
-        <x:v>A查看共享预验收与问题单</x:v>
+        <x:v>A已签执行事实；B不代签</x:v>
       </x:c>
       <x:c r="F12" s="23" t="str">
-        <x:v>B_DB06_PREACCEPTANCE_20260830.md</x:v>
+        <x:v>DB06_关系修复待B复核_20260831.md</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="32" customHeight="1">
@@ -658,16 +658,16 @@
         <x:v>全部条件闭环后PASS</x:v>
       </x:c>
       <x:c r="C13" s="24" t="str">
-        <x:v>页面搭建完成；模型关系与证据未闭环</x:v>
+        <x:v>A侧关系阻塞已解除；待B独立复核</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>READY_B_REVIEW</x:v>
       </x:c>
       <x:c r="E13" s="24" t="str">
-        <x:v>保持G3 BLOCKED，不虚报最终PASS</x:v>
+        <x:v>G3在B签收前不改正式PASS</x:v>
       </x:c>
       <x:c r="F13" s="24" t="str">
-        <x:v>DB06_ACCEPTANCE_V50.txt</x:v>
+        <x:v>DB06_关系修复待B复核_20260831.md</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -682,7 +682,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re20569ffc54940fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R340b08a4615d4ea8"/>
   </x:tableParts>
 </x:worksheet>
 </file>